--- a/output/featured.xlsx
+++ b/output/featured.xlsx
@@ -418,15 +418,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -470,28 +470,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Kaun Kitney Panee Mein</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>featured/1/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>featured/700/Kaun Kitney Panee Mein.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zdRgTpqhGaY</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -501,28 +505,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rescue Dawn</t>
+          <t>Jazbaa: Advocate Anuradha Varma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>featured/1/Rescue Dawn.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>featured/700/Jazbaa Advocate Anuradha Varma.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oKTbF2ZFpi8</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -532,12 +540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aaahladam</t>
+          <t>Viswasam Athalle Ellam</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -546,14 +554,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>featured/1/Aaahladam.jpg</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>featured/700/Viswasam Athalle Ellam.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nBHI346o25Y</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -563,28 +575,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Kunjiramayanam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>featured/1/Trikala Script of God.jpg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>featured/700/Kunjiramayanam.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wIE1iBDU7II</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -594,28 +610,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Dummy Tappasu</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>featured/1/Blast Zone.jpg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>featured/700/Dummy Tappasu.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=n64cVDMt6JE</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -625,12 +645,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Cinema Chupista Maava</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -639,14 +659,18 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>featured/1/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>featured/700/Cinema Chupista Maava.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8HLUF1ODuys</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -656,28 +680,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Charlie Kay Chakkar Mein</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>featured/1/Sandigdham.jpg</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>featured/700/Charlie Kay Chakkar Mein.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RHzVCdpXBDc</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -687,28 +715,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Exorcism Of Emily Rose</t>
+          <t>Kaththukkutti</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>featured/1/The Exorcism Of Emily Rose.jpg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>featured/700/Kaththukkutti.jpg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k2Zy5pFjy24</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -718,28 +750,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Keechaka</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>featured/1/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>featured/700/Keechaka.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vcaTBXkqv24</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -749,28 +785,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>featured/1/Purushaha.jpg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>featured/700/Phantom.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1G3uXwhx_uk</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -780,28 +820,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Utopiayile Rajavu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>featured/1/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>featured/700/Utopiayile Rajavu.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EyS__WVRUgM</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -811,28 +855,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nawab Cafe</t>
+          <t>Puli</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>featured/1/Nawab Cafe.jpg</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>featured/700/Puli.jpg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U9kCY9psgOc</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -842,28 +890,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Chinar Daastaan-E-Ishq</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>featured/1/Godari Gattupaina.jpg</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>featured/700/Chinar Daastaan-E-Ishq.jpg</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=f7hHiLG8XGE</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -873,28 +925,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>First Time</t>
+          <t>Ennu Ninte Moideen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>featured/1/First Time.jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>featured/700/Ennu Ninte Moideen.jpg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3WysfWXNw64</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -904,28 +960,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Kis Kisko Pyaar Karu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>featured/1/Ramani Kalyanam.jpg</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>featured/700/Kis Kisko Pyaar Karu.jpg</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Xhmej50EGM8</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -935,28 +995,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lee Cronin’s The Mummy</t>
+          <t>Main Aur Charles</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>700</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>featured/1/Lee Cronin’s The Mummy.jpg</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>featured/700/Main Aur Charles.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wOF9MlEOfuE</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -966,28 +1030,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nawab Cafe</t>
+          <t>Guddu Ki Gun</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>featured/2/Nawab Cafe.jpg</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>featured/701/Guddu Ki Gun.jpg</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Zf5S3ntloBk</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -997,28 +1065,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Bangistan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>featured/2/Leader.jpg</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>featured/701/Bangistan.jpg</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uPtyOoYL12Y</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1028,12 +1100,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Columbus</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1042,14 +1114,18 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>featured/2/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>featured/701/Columbus.jpg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=87KHSGbe6ho</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1059,12 +1135,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Masala Padam</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1073,14 +1149,18 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>featured/2/Leader.jpg</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>featured/701/Masala Padam.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iVyNjajUq9k</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1090,12 +1170,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Madhura Naranga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1104,14 +1184,18 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>featured/2/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>featured/701/Madhura Naranga.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ju-t2hzTWwQ</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1121,28 +1205,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Wedding Pullav</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>featured/2/Leader.jpg</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>featured/701/Wedding Pullav.jpg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jhBQXc1bJAs</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1152,28 +1240,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Succubus</t>
+          <t>Bhaag Johnny</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>featured/2/Succubus.jpg</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>featured/701/Bhaag Johnny.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZybkdyM-Y5g</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1183,28 +1275,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Moneyball</t>
+          <t>Hogaya Dimaagh Ka Dahi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>featured/2/Moneyball.jpg</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>featured/701/Hogaya Dimaagh Ka Dahi.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tQkM-5AKfXU</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1214,28 +1310,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karikaada</t>
+          <t>Kai Raja Kai</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>featured/2/Karikaada.jpg</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>featured/701/Kai Raja Kai.jpg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Av2_tsJSV5c</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1245,28 +1345,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Jamna Pyari</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>featured/2/Kara.jpg</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>featured/701/Jamna Pyari.jpg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OUhMcOv821U</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1276,28 +1380,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Race</t>
+          <t>Jigina</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>featured/2/The Race.jpg</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>featured/701/Jigina.jpg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D47P1gOKecc</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1307,28 +1415,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mr and Mrs Bachelor</t>
+          <t>Acha Din</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>featured/2/Mr and Mrs Bachelor.jpg</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>featured/701/Acha Din.jpg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XBrWYwHNIt8</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1338,28 +1450,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Jawani Phir Nahi Ani</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>featured/2/Kara.jpg</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>featured/701/Jawani Phir Nahi Ani.jpg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=btB6WQz6xhE</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1369,28 +1485,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Reclaim</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>featured/2/Kara.jpg</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>featured/701/Reclaim.jpg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Kk7XQqWy2VU</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1400,12 +1520,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spa</t>
+          <t>Lokha Samastha</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1414,14 +1534,18 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>featured/2/Spa.jpg</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>featured/701/Lokha Samastha.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O3mHFd3MMj0</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1431,29 +1555,7558 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brothers and Sisters Season 1</t>
+          <t>Daagdi Chaawl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>701</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>featured/2/Brothers and Sisters Season 1.jpg</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>featured/701/Daagdi Chaawl.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9y5ImqDEeJo</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Puli</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>702</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>featured/702/Puli.jpg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U9kCY9psgOc</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Yatchan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>702</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>featured/702/Yatchan.jpg</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ni1cvXUpv-I</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Maanga</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>702</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>featured/702/Maanga.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3K7GZBsdSLg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Puli</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>702</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>featured/702/Puli.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U9kCY9psgOc</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Savaale Samaali</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>702</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>featured/702/Savaale Samaali.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9qvjiFbB8U8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sabse Badhkar Hum 2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>702</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>featured/702/Sabse Badhkar Hum 2.jpg</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aYrj0-dXpl8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kirum</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>702</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>featured/702/Kirum.jpg</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gMC8kkwbIQQ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>49-O</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>702</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>featured/702/49-O.jpg</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fwt8CWA35qw</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chandrika</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>702</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>featured/702/Chandrika.jpg</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uCseAkQZqgA</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Singh Is Bliing</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>702</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>featured/702/Singh Is Bliing.jpg</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J6HIAfNxzQk</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Talvar</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>702</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>featured/702/Talvar.jpg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aQNMsw8Ljjc</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Calendar Girls</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>702</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>featured/702/Calendar Girls.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zmpYu4-Gk94</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>702</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>featured/702/Lavender.jpg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=L6OMsLU7Ikc</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Karachi se Lahore</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>702</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>featured/702/Karachi se Lahore.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WkHsPQjGxNw</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kuttram Kadithal</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>702</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>featured/702/Kuttram Kadithal.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=urarX9X0LjA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Maanikya</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>702</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>featured/702/Maanikya.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-VVm4Z6qzys</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>8th March</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>703</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>featured/703/8th March.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HHFt0V8upT0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Subramanyam For Sale</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>703</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>featured/703/Subramanyam For Sale.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RamHxtj5Hr4</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kis Kisko Pyaar Karu</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>703</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>featured/703/Kis Kisko Pyaar Karu.jpg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Xhmej50EGM8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Bhaag Johnny</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>703</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>featured/703/Bhaag Johnny.jpg</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZybkdyM-Y5g</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Meeruthiya Gangsters</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>703</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>featured/703/Meeruthiya Gangsters.jpg</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kamXBKVctrg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ketugadu</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>703</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>featured/703/Ketugadu.jpg</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NcbyJ3b8oXo</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Thakka Thakka</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>703</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>featured/703/Thakka Thakka.jpg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l6kgGQS9B9Y</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sahasam Seyyara Dimbaka</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>703</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>featured/703/Sahasam Seyyara Dimbaka.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qaANVefyMPs</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KL 10 Pathu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>703</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>featured/703/KL 10 Pathu.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PKHmB-ehdHU</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Love 24×7</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>703</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>featured/703/Love 24×7.jpg</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IDf14F02a6o</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>All Is Well</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>703</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>featured/703/All Is Well.jpg</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wlyc0NxmRYs</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Katti Batti</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>703</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>featured/703/Katti Batti.jpg</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EYTsvOp13K0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MSG-2 The Messenger</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>703</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>featured/703/MSG-2 The Messenger.jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2OxIWWcPgxc</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Samrajyam 2: Son of Alexander</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>703</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>featured/703/Samrajyam 2 Son of Alexander.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MztAvNiZ5UE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kanthari</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>703</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>featured/703/Kanthari.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1kHtg0S77oI</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Beeruva</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>703</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>featured/703/Beeruva.jpg</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lgFNurSQAxg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cinema Chupista Maava</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>704</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>featured/704/Cinema Chupista Maava.jpg</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8HLUF1ODuys</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Hora Hori</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>704</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>featured/704/Hora Hori.jpg</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NFgjYn-RZ5w</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Baankey Ki Crazy Baraat</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>704</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>featured/704/Baankey Ki Crazy Baraat.jpg</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iG6Db4aASOQ</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Vaalu</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>704</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>featured/704/Vaalu.jpg</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S58EI1VtwaQ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bale Bale Magadivoy</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>704</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>featured/704/Bale Bale Magadivoy.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UZ6LvBnzLMw</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Uppi 2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>704</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>featured/704/Uppi 2.jpg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YL0HDKMauHs</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Kill ’em All</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>704</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>featured/704/Kill ’em All.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IUjHCStZugo</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Chandi Veeran</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>704</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>featured/704/Chandi Veeran.jpg</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LThuhD1iCGc</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Malini &amp; Co</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>704</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>featured/704/Malini &amp; Co.jpg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uGkArp7C-Jo</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Naalu Policeum Nalla Irundha Oorum</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>704</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>featured/704/Naalu Policeum Nalla Irundha Oorum.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4Ty3ndY-s7A</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Marathi</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>704</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>featured/704/Court.jpg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4sc8z7zav9A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nirnayakam</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>704</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>featured/704/Nirnayakam.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0HwffIMNEEA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Appavum Veenjum</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>704</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>featured/704/Appavum Veenjum.jpg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-nfAqLCv5KU</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Phantom</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>704</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>featured/704/Phantom.jpg</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1G3uXwhx_uk</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>32aam Adhyayam 23aam Vaakyam</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>704</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>featured/704/32aam Adhyayam 23aam Vaakyam.jpg</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1rjQZghCDyo</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Swargathekkal Sundaram</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>705</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>featured/705/Swargathekkal Sundaram.jpg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iLPkQ8o3G48</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>All Is Well</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>705</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>featured/705/All Is Well.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wlyc0NxmRYs</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Orange Mittai</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>705</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>featured/705/Orange Mittai.jpg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wo5HjdH_BYU</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Maari</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>705</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>featured/705/Maari.jpg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W3XFChOz-Z0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>I Love New Year</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>705</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>featured/705/I Love New Year.jpg</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GYFT2aiDkjI</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Thoda Lutf Thoda Ishq</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>705</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>featured/705/Thoda Lutf Thoda Ishq.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3-vX7GW0X3A</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Mooch</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>705</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>featured/705/Mooch.jpg</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6b2v46syjCQ</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cinema Chupista Maava</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>705</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>featured/705/Cinema Chupista Maava.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8HLUF1ODuys</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Upendra 2</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>705</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>featured/705/Upendra 2.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YL0HDKMauHs</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Thinkal Muthal Velli Vare</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>705</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>featured/705/Thinkal Muthal Velli Vare.jpg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J8RCGyvHcRc</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jaanisaar</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>705</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>featured/705/Jaanisaar.jpg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6vd9tjw2b4M</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mantra 2</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>705</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>featured/705/Mantra 2.jpg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mj0m6h-C2ZE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Bangistan</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>705</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>featured/705/Bangistan.jpg</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uPtyOoYL12Y</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Pandavulu Okkadu</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>705</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>featured/705/Pandavulu Okkadu.jpg</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0QXJBHa22ek</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nee-Na</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>705</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>featured/705/Nee-Na.jpg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6u_xDgOd1s</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Pramadam Chavu 100%</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>705</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>featured/705/Pramadam Chavu 100%.jpg</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3nV6ae2grvs</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Acharam</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>706</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>featured/706/Acharam.jpg</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7CTs8D2tsP8</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mohini The Heroine</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>706</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>featured/706/Mohini The Heroine.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4-j7wyf8rQ4</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sir C.P</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>706</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>featured/706/Sir C.P.jpg</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-KLUkQE3CDU</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Masaan</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>706</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>featured/706/Masaan.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SKJfBo3xMW0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Kshatriya</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>706</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>featured/706/Kshatriya.jpg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E_isQCI4YNI</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Palakkattu Madhavan</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>706</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>featured/706/Palakkattu Madhavan.jpg</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=D2719wGM8Vw</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Thoda Lutf Thoda Ishq</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>706</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>featured/706/Thoda Lutf Thoda Ishq.jpg</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3-vX7GW0X3A</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Njan Steve Lopez</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>706</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>featured/706/Njan Steve Lopez.jpg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X2OyKsF6Tq4</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Bhaskar the Rascal</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>706</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>featured/706/Bhaskar the Rascal.jpg</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s7FGizXmo-s</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Tanu Weds Manu Returns</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>706</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>featured/706/Tanu Weds Manu Returns.jpg</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wGGmyaurjAI</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Agyaat</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>706</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>featured/706/Agyaat.jpg</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HZ-Ohr0iQOE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Basthi</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>706</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>featured/706/Basthi.jpg</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3jlzeaOLLIk</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Indru Netru Naalai</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>706</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>featured/706/Indru Netru Naalai.jpg</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6YnVOsmfBQU</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Seenugadi Love Story</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>706</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>featured/706/Seenugadi Love Story.jpg</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FcTdN31DFmk</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Lailaa O Lailaa</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>706</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>featured/706/Lailaa O Lailaa.jpg</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8iwxpjzyLFA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Bezubaan Ishq</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>706</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>featured/706/Bezubaan Ishq.jpg</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DNnMjx1WeAw</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>I Love NY</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>707</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>featured/707/I Love NY.jpg</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GYFT2aiDkjI</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Moone Moonu Varthai</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>707</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>featured/707/Moone Moonu Varthai.jpg</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zYGgV75l9hE</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Bombay Velvet</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>707</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>featured/707/Bombay Velvet.jpg</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AmMIQZ1TAig</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Ennum Eppozhum</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>707</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>featured/707/Ennum Eppozhum.jpg</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bL5KBVY7lOw</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>36 Vayadhinile</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>707</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>featured/707/36 Vayadhinile.jpg</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LOEqjt533WY</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Uvaa</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>707</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>featured/707/Uvaa.jpg</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e9vnNUFlblc</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Where Is Vidya Balan</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>707</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>featured/707/Where Is Vidya Balan.jpg</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d30BjKI2Vo8</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Eli</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>707</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>featured/707/Eli.jpg</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qfSTiAw1rkM</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Yahaan Sabki Lagi Hai</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>707</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>featured/707/Yahaan Sabki Lagi Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IKBDC8SlLWc</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Vinavayya Ramayya</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>707</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>featured/707/Vinavayya Ramayya.jpg</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A49k6jtaMoI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tippu</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>707</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>featured/707/Tippu.jpg</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Mb49Id8j4G4</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Lava Kusa</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>707</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>featured/707/Lava Kusa.jpg</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Bjnf-gCazEE</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Kerintha</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>707</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>featured/707/Kerintha.jpg</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zdjqWHj65Uk</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3 A.M.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>707</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>featured/707/3 A.M..jpg</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Dk5FxcLqaGw</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Singham 123</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>707</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>featured/707/Singham 123.jpg</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CagWG7cEWHI</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Chal Guru Ho Ja Shuru</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>707</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>featured/707/Chal Guru Ho Ja Shuru.jpg</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9KRBf6eCctE</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Dhee Ante Dhee</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>708</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>featured/708/Dhee Ante Dhee.jpg</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BAWRUR15bq8</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Kallappadam</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>708</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>featured/708/Kallappadam.jpg</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vLFpSYCfxFU</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mahabalipuram</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>708</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>featured/708/Mahabalipuram.jpg</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zcC7SPDCwqY</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Yentha Vaadu Gaanie</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>708</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>featured/708/Yentha Vaadu Gaanie.jpg</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qJJreikjEYs</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ivan Maryadaraman</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>708</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>featured/708/Ivan Maryadaraman.jpg</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GgQ-vJnX5sY</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Tanu Weds Manu Returns</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>708</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>featured/708/Tanu Weds Manu Returns.jpg</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wGGmyaurjAI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Vethu Vettu</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>708</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>featured/708/Vethu Vettu.jpg</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MX-rSB1MIPM</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>O Kadhal Kanmani</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>708</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>featured/708/O Kadhal Kanmani.jpg</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2mBG4vlhcCc</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Vai Raja Vai</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>708</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>featured/708/Vai Raja Vai.jpg</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gZhj9cZHum8</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Thottal Thodarum</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>708</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>featured/708/Thottal Thodarum.jpg</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tuNoQH_j4VI</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Bombay Velvet</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>708</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>featured/708/Bombay Velvet.jpg</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N3fLma56kI0</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sagaptham</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>708</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>featured/708/Sagaptham.jpg</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sH9HN3c_cSU</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Barkhaa</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>708</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>featured/708/Barkhaa.jpg</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JbVtdWOFZS4</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dongaata</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>708</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>featured/708/Dongaata.jpg</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Or4skjkMbpQ</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Namasthe Bali Island</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>708</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>featured/708/Namasthe Bali Island.jpg</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SNphwjfQEjM</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Bench Talkies</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>709</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>featured/709/Bench Talkies.jpg</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dBzXzjScAwQ</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Naalo Okkadu</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>709</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>featured/709/Naalo Okkadu.jpg</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QkNxfliJ92k</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Coffee Bloom</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>709</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>featured/709/Coffee Bloom.jpg</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zt64Maw5WSU</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Village Guys</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>709</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>featured/709/Village Guys.jpg</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=shTwcnalGyU</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Hunterrr</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>709</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>featured/709/Hunterrr.jpg</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ytDp30vuiCo</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Kaagaz Ke Fools</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>709</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>featured/709/Kaagaz Ke Fools.jpg</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lna6_pkNaYE</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kadavul Paathi Mirugam Paathi</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>709</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>featured/709/Kadavul Paathi Mirugam Paathi.jpg</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=APLqb5tCquk</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Thimmiri</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>709</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>featured/709/Thimmiri.jpg</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ax7fY75wLGI</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>The Reporter</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>709</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>featured/709/The Reporter.jpg</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ggwwSL6hTGI</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Kaai Raja Kaai</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>709</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>featured/709/Kaai Raja Kaai.jpg</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W43-8R5eiXE</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Aadu</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>709</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>featured/709/Aadu.jpg</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_jlVhEs75Fo</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Dum</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>709</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>featured/709/Dum.jpg</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dXdVIXHa0HI</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Four Two Ka One</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>709</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>featured/709/Four Two Ka One.jpg</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5oZPuQPA1gA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Thoppi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>710</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>featured/710/Thoppi.jpg</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kVGNZBAX96s</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jai Ho Democracy</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>710</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>featured/710/Jai Ho Democracy.jpg</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JG5QdPMe_9c</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Thunai Mudhalvar</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>710</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>featured/710/Thunai Mudhalvar.jpg</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Bl6Y3j7Mvz8</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Vaaradhi</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>710</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>featured/710/Vaaradhi.jpg</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A__SUiu8DIM</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Miss Leelavathi</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>710</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>featured/710/Miss Leelavathi.jpg</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jZWVsWZ56dQ</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Riyasat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>710</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>featured/710/Riyasat.jpg</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iwa147RIsjg</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>NH10</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>710</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>featured/710/NH10.jpg</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A9icNqWlylw</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Dirty Politics</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>710</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>featured/710/Dirty Politics.jpg</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a8ipZ75Gp1s</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Budugu</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>710</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>featured/710/Budugu.jpg</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9sINxibjEEk</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Vaanavil Vaazhkai</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>710</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>featured/710/Vaanavil Vaazhkai.jpg</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XObuB5pcmRY</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Valiyavan</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>710</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>featured/710/Valiyavan.jpg</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ClWSw3ZXzoo</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Dharani</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>710</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>featured/710/Dharani.jpg</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PwHHeqUy18Y</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Katham Katham</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>710</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>featured/710/Katham Katham.jpg</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7Zpp_vv1us4</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Hawaizaada</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>710</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>featured/710/Hawaizaada.jpg</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pjtN0IV_lJc</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Rajathandhiram</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>710</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>featured/710/Rajathandhiram.jpg</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NlI3H_udS6w</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Ek Paheli Leela</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>710</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>featured/710/Ek Paheli Leela.jpg</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=azRVCV2k3Uc</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Barkha</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>711</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>featured/711/Barkha.jpg</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JbVtdWOFZS4</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Haram</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>711</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>featured/711/Haram.jpg</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4zw8mdKE0d0</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>August 2</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>711</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>featured/711/August 2.jpg</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ww0HQFE4wHU</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Dolly Ki Doli</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>711</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>featured/711/Dolly Ki Doli.jpg</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uzdu62XspwY</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Rey</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>711</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>featured/711/Rey.jpg</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zgoxa0wHRQY</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Khamoshiyan</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>711</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>featured/711/Khamoshiyan.jpg</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-tBWvbyIiVM</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Janda Pai Kapiraju</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>711</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>featured/711/Janda Pai Kapiraju.jpg</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pfDiobR95p0</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Shamitabh</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>711</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>featured/711/Shamitabh.jpg</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Bds5Qr9BR2w</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Roy</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>711</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>featured/711/Roy.jpg</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ahz3kTiGo3s</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Dilliwaali Zaalim Girlfriend</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>711</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>featured/711/Dilliwaali Zaalim Girlfriend.jpg</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NjYG9ccLD0A</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Pesarattu</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>711</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>featured/711/Pesarattu.jpg</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=woLlNhBZOwI</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Pyaar Hawas Dhokha</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>711</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>featured/711/Pyaar Hawas Dhokha.jpg</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s1n4-x60wac</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Simhamanti Chinnodu</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>711</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>featured/711/Simhamanti Chinnodu.jpg</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9J5TOtcOTlg</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Dr. Saleem</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>711</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>featured/711/Dr. Saleem.jpg</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UnHghWfL1Ik</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>NH10</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>711</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>featured/711/NH10.jpg</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A9icNqWlylw</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Yennai Arindhaal</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>711</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>featured/711/Yennai Arindhaal.jpg</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=B7c87SWQg-Y</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Vajram</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>712</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>featured/712/Vajram.jpg</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qU2tt9n096w</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Badmashiyaan</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>712</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>featured/712/Badmashiyaan.jpg</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w88ybSgyERQ</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Dirty Politics</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>712</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>featured/712/Dirty Politics.jpg</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gQ2hV068SYU</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Anekudu</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>712</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>featured/712/Anekudu.jpg</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BTpdE9YyTE4</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Surya vs Surya</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>712</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>featured/712/Surya vs Surya.jpg</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PX3X6dirZG0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Monsoon</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>712</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>featured/712/Monsoon.jpg</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AwRKghsax4k</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>JK Enum Nanbanin Vaazhkai</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>712</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>featured/712/JK Enum Nanbanin Vaazhkai.jpg</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fMJ21v7mX7U</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Hey Bro</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>712</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>featured/712/Hey Bro.jpg</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wu55BQG-W7M</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Ram Leela</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>712</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>featured/712/Ram Leela.jpg</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YQPfeinXxcA</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Pisachi</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>712</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>featured/712/Pisachi.jpg</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JXNDRjSVVZI</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Mitwaa</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Marathi</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>712</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>featured/712/Mitwaa.jpg</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RzRMeBxRNVg</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Bham Bolenath</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>712</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>featured/712/Bham Bolenath.jpg</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8inxztzBlL4</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Paddanandi Premalo Mari</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>712</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>featured/712/Paddanandi Premalo Mari.jpg</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HfYN9tE8_XY</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Aamayum Muyalum</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>712</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>featured/712/Aamayum Muyalum.jpg</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4tV5lK488v8</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Ab Tak Chhappan 2</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>712</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>featured/712/Ab Tak Chhappan 2.jpg</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fbmoxgla0Pg</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Aa Intlo Deyyam Uvnda</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>712</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>featured/712/Aa Intlo Deyyam Uvnda.jpg</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yLQ2PLKEkgU</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Cousins</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>713</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>featured/713/Cousins.jpg</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_jnYktU5lj8</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>I (Ai)</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>713</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>featured/713/I (Ai).jpg</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8uPK9Ov6Zd4</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Ladies and Gentlemen</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>713</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>featured/713/Ladies and Gentlemen.jpg</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=frUz99EBeMo</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Roy</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>713</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>featured/713/Roy.jpg</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ahz3kTiGo3s</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Hum Tum Dushman Dushman</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>713</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>featured/713/Hum Tum Dushman Dushman.jpg</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nzh0jNXAeXk</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>MSG: The Messenger</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>713</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>featured/713/MSG The Messenger.jpg</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=scuWiXG5bh8</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Balkadu</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Marathi</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>713</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>featured/713/Balkadu.jpg</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T0KpFIAf4_M</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Vishayam Veliya Theriya koodathu</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>713</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>featured/713/Vishayam Veliya Theriya koodathu.jpg</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UoY_J8NDU1s</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Malli Malli Idi Rani Roju</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>713</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>featured/713/Malli Malli Idi Rani Roju.jpg</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=KXKZbb-loBQ</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Gaddam Gang</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>713</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>featured/713/Gaddam Gang.jpg</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Sne74sTpXac</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Shamitabh</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>713</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>featured/713/Shamitabh.jpg</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Bds5Qr9BR2w</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Lokmanya: Ek Yugpurush</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Marathi</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>713</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>featured/713/Lokmanya Ek Yugpurush.jpg</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lRSrvLOMJoQ</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Touring Talkies</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>713</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>featured/713/Touring Talkies.jpg</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iYYrCMfiTNw</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Action Jackson</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>713</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>featured/713/Action Jackson.jpg</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YubQzbzGHps</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>713</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>featured/713/Baby.jpg</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-Yu_2nyOP5o</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Dolly Ki Doli</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>713</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>featured/713/Dolly Ki Doli.jpg</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RTLZdQyydg8</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Crazy Cukkad Family</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>714</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>featured/714/Crazy Cukkad Family.jpg</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CJz1hdiuMiI</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sulemani Keeda</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>714</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>featured/714/Sulemani Keeda.jpg</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BANLA5CzK-U</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>A Shyam Gopal Varma Film</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>714</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>featured/714/A Shyam Gopal Varma Film.jpg</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0gdrPhmkoQw</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sharafat Gayi Tel Lene</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>714</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>featured/714/Sharafat Gayi Tel Lene.jpg</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tWKukOLeYp0</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>I (Ai)</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>714</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>featured/714/I (Ai).jpg</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8uPK9Ov6Zd4</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>I (Ai)</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>714</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>featured/714/I (Ai).jpg</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8uPK9Ov6Zd4</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Encounter Shankar</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>714</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>featured/714/Encounter Shankar.jpg</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S8kZqkZfGJ8</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Njangalude Veettile Adhithikal</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>714</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>featured/714/Njangalude Veettile Adhithikal.jpg</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=isgC48eyy8Q</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>To Noora with Love</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>714</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>featured/714/To Noora with Love.jpg</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=CZt0vOf2Zvg</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Mumbai Can Dance Saala</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>714</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>featured/714/Mumbai Can Dance Saala.jpg</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y-wc7k4yTt4</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Raktharakshassu 3D</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>714</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>featured/714/Raktharakshassu 3D.jpg</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Cy_0r5TDYU8</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Dangerous Khiladi 4</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>714</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>featured/714/Dangerous Khiladi 4.jpg</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XwuQzIXnS2g</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Iyobinte Pusthakam</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>714</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>featured/714/Iyobinte Pusthakam.jpg</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IbD5Baz0kOI</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>714</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>featured/714/PK.jpg</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SOXWc32k4zA</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Ugly</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>714</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>featured/714/Ugly.jpg</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4ougQY2-zpk</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Chandrakala</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>714</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>featured/714/Chandrakala.jpg</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=61Uhu2odb5M</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Badlapur Boys</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>715</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>featured/715/Badlapur Boys.jpg</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ps0lUNMK5bY</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Main Aur Mr. Riight</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>715</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>featured/715/Main Aur Mr. Riight.jpg</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6WKUJ5zb_Tw</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Bhopal: A Prayer for Rain</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>715</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>featured/715/Bhopal A Prayer for Rain.jpg</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rO6xCAsv4s4</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Zed Plus</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>715</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>featured/715/Zed Plus.jpg</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dwQ2egQe82Y</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Action Jackson</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>715</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>featured/715/Action Jackson.jpg</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YubQzbzGHps</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Titoo MBA</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>715</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>featured/715/Titoo MBA.jpg</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nx8IEEOG2c4</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Yamaleela 2</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>715</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>featured/715/Yamaleela 2.jpg</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=De7lDPwyy5I</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Zid</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>715</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>featured/715/Zid.jpg</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bArdCUba1EI</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Na Bangaaru Talli</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>715</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>featured/715/Na Bangaaru Talli.jpg</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QZ1P4bCfm8M</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Velmurugan Borewells</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>715</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>featured/715/Velmurugan Borewells.jpg</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qQhs9YgMkAU</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Ice Cream 2</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>715</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>featured/715/Ice Cream 2.jpg</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jHA72BWY96M</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Pilla Nuvvu Leni Jeevitham</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>715</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>featured/715/Pilla Nuvvu Leni Jeevitham.jpg</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NQMrOS9UN-E</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -1496,7 +9149,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>

--- a/output/featured.xlsx
+++ b/output/featured.xlsx
@@ -421,12 +421,12 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Momacu</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,14 +488,10 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>featured/1/Momacu.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ebWqjLUBgqE</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -505,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +511,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,14 +519,10 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>featured/1/Maa Behen.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -540,17 +532,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Premam Madhuram</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,14 +550,10 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>featured/1/Premam Madhuram.jpg</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=RkMt3-2m2mw</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Peddi.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -575,7 +563,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +573,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,14 +581,10 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>featured/1/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -610,17 +594,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,14 +612,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>featured/1/Beast of War.jpg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -645,7 +625,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +635,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,14 +643,10 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>featured/1/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ZmPVwT_R_eI</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -680,12 +656,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rescue Dawn</t>
+          <t>Momacu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -698,14 +674,10 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>featured/1/Rescue Dawn.jpg</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=UNm9Tzo5rvI</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Momacu.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -715,17 +687,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aaahladam</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,14 +705,10 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>featured/1/Aaahladam.jpg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=ciF1rVqYX9E</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -750,17 +718,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Premam Madhuram</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,14 +736,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>featured/1/Trikala Script of God.jpg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Premam Madhuram.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -785,7 +749,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +759,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,14 +767,10 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>featured/1/Blast Zone.jpg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -820,17 +780,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,14 +798,10 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>featured/1/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -855,7 +811,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -873,14 +829,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>featured/1/Sandigdham.jpg</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -890,12 +842,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Exorcism Of Emily Rose</t>
+          <t>Rescue Dawn</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -908,14 +860,10 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>featured/1/The Exorcism Of Emily Rose.jpg</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=Bi-PLwxwvy8</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Rescue Dawn.jpg</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -925,17 +873,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Aaahladam</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,14 +891,10 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>featured/1/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Aaahladam.jpg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -960,7 +904,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -978,14 +922,10 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>featured/1/Purushaha.jpg</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Trikala Script of God.jpg</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -995,7 +935,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +945,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,14 +953,10 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>featured/1/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=6IxPD-jNdwM</t>
-        </is>
-      </c>
+          <t>featured/06-04-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026-06-04</t>

--- a/output/featured.xlsx
+++ b/output/featured.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,20 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/KD The Devil.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>featured/06-05-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=647TsP9EP-0</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,20 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/29.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>featured/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -550,20 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Peddi.jpg</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>featured/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -573,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -581,20 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Patriot.jpg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>featured/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Office Romance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -604,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -612,20 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Sattendru Maarudhu Vaanilai.jpg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>featured/06-05-2026/Office Romance.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>The Marked Woman</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -635,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -643,20 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Patriot.jpg</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>featured/06-05-2026/The Marked Woman.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=161b4xLkokE</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Momacu</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -666,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -674,20 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Momacu.jpg</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>featured/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -697,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -705,30 +733,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Maa Behen.jpg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>featured/06-05-2026/Sukhamano Sukhamann.jpg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Premam Madhuram</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -736,20 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Premam Madhuram.jpg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>featured/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -767,30 +803,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>featured/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -798,10 +838,9 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Beast of War.jpg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>featured/06-04-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -811,7 +850,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -829,10 +868,9 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>featured/06-04-2026/29.jpg</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -842,17 +880,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rescue Dawn</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -860,10 +898,9 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Rescue Dawn.jpg</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>featured/06-04-2026/Peddi.jpg</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -873,17 +910,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aaahladam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -891,10 +928,9 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Aaahladam.jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>featured/06-04-2026/Patriot.jpg</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -904,7 +940,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -914,7 +950,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -922,10 +958,9 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>featured/06-04-2026/Trikala Script of God.jpg</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>featured/06-04-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-06-04</t>
@@ -935,29 +970,328 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Momacu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Momacu.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Maa Behen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Premam Madhuram</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Premam Madhuram.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Carmeni Selvam</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carmeni Selvam</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Rescue Dawn</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Rescue Dawn.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aaahladam</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Aaahladam.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trikala: Script of God</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>featured/06-04-2026/Trikala Script of God.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Blast Zone</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Telugu</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>featured/06-04-2026/Blast Zone.jpg</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
@@ -974,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -996,10 +1330,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>16</v>
       </c>
     </row>
